--- a/data/IDL List Oct2026.xlsx
+++ b/data/IDL List Oct2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VietBao.Nguyen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F60AAAF-C61E-4193-811C-1DF5CE2C0C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF85B54-D299-4086-BBF7-B6E05BE2BD92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="341">
   <si>
     <t>Employee Code</t>
   </si>
@@ -1037,6 +1037,12 @@
   </si>
   <si>
     <t>ThiNgocGiau.Vo@ttigroup.com.vn</t>
+  </si>
+  <si>
+    <t>Phạm Ngọc Tú Trinh</t>
+  </si>
+  <si>
+    <t>Đỗ Văn Lợi</t>
   </si>
 </sst>
 </file>
@@ -1183,7 +1189,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="IDLListSep2026Updated" displayName="IDLListSep2026Updated" ref="A1:I105" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="IDLListSep2026Updated" displayName="IDLListSep2026Updated" ref="A1:I106" totalsRowShown="0">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Employee Code"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Full name"/>
@@ -1394,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I105"/>
+  <dimension ref="A1:I106"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -4435,6 +4441,33 @@
         <v>338</v>
       </c>
     </row>
+    <row r="106" spans="1:9">
+      <c r="A106" s="9">
+        <v>530178</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E106" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="G106" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I106" s="7"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
